--- a/FC와디즈_능력치.xlsx
+++ b/FC와디즈_능력치.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">

--- a/FC와디즈_능력치.xlsx
+++ b/FC와디즈_능력치.xlsx
@@ -472,13 +472,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:K19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col width="10.7109375" customWidth="1" style="2" min="1" max="1"/>
     <col width="14.42578125" bestFit="1" customWidth="1" style="3" min="11" max="11"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" customFormat="1" s="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -541,10 +542,10 @@
         <v>10</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>11</v>
@@ -578,10 +579,10 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>10</v>
@@ -982,6 +983,8 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>

--- a/FC와디즈_능력치.xlsx
+++ b/FC와디즈_능력치.xlsx
@@ -563,7 +563,7 @@
         <v>13</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>8</v>
@@ -637,7 +637,7 @@
         <v>19</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>16</v>
@@ -822,7 +822,7 @@
         <v>12</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>10</v>
@@ -859,7 +859,7 @@
         <v>8</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>20</v>
@@ -970,7 +970,7 @@
         <v>18</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>14</v>
